--- a/Allgemeine Daten/covariate/generation/flea_jumplength_bloodmeal_raw.xlsx
+++ b/Allgemeine Daten/covariate/generation/flea_jumplength_bloodmeal_raw.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/vorlesungen/Allgemeine Daten/covariate/generation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F196C0-51F8-B34D-9E16-A6B6306773A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC3B47D-2436-C447-89EB-7379F59943D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2400" yWindow="600" windowWidth="36000" windowHeight="19960" xr2:uid="{A5B12C49-1460-7B46-AA19-811389EE84C0}"/>
   </bookViews>
@@ -892,67 +892,67 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>0.45168729717598888</c:v>
+                  <c:v>3.7591179150939049</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.0756635501259266</c:v>
+                  <c:v>1.7095957884132167</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.0033366151363126</c:v>
+                  <c:v>4.9699578977173475</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.881881698168943</c:v>
+                  <c:v>3.2029638995228402</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.3443305073286931</c:v>
+                  <c:v>4.8547439657154445</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.4467401747441766</c:v>
+                  <c:v>4.3064289747389148</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6102013621769631</c:v>
+                  <c:v>3.4256601285009838</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.781893123384056</c:v>
+                  <c:v>7.0778241275773652</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.2408347184285287</c:v>
+                  <c:v>7.7718210768435725</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.4099029260760432</c:v>
+                  <c:v>10.276280325241784</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15.198330686024249</c:v>
+                  <c:v>5.5978330941288608</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.8728290538969361</c:v>
+                  <c:v>8.6666405250777352</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.8939607560292355</c:v>
+                  <c:v>9.9397158478171583</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14.0418411998536</c:v>
+                  <c:v>11.526183320662803</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.9824680144743567</c:v>
+                  <c:v>12.442321152332408</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12.85002960294872</c:v>
+                  <c:v>14.501056799790037</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12.237381215977994</c:v>
+                  <c:v>13.463676090460151</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>12.59520644466159</c:v>
+                  <c:v>15.131940487488912</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16.436315382084317</c:v>
+                  <c:v>14.801243356533993</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>15.581304581083794</c:v>
+                  <c:v>12.879261700525404</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>16.719296715959274</c:v>
+                  <c:v>15.009082151610302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1260,6 +1260,457 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$C$2:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$F$2:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>24.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>13.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19.100000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7668-4F44-924A-26AC901341EA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="610644671"/>
+        <c:axId val="610647359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="610644671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE"/>
+                  <a:t>Bloodmeal</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="610647359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="610647359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE"/>
+                  <a:t>Jumplength</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="610644671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1340,6 +1791,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1857,6 +2348,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2441,6 +3448,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>309034</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>16934</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>732367</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>118534</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Diagramm 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CE1B845-E176-074A-AF8F-FF35A68B7CB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2816,7 +3859,7 @@
       </c>
       <c r="E2" s="1">
         <f ca="1">2+1.2*C2+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>0.45168729717598888</v>
+        <v>3.7591179150939049</v>
       </c>
       <c r="F2">
         <v>24.1</v>
@@ -2849,7 +3892,7 @@
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:E22" ca="1" si="0">2+1.2*C3+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>6.0756635501259266</v>
+        <v>1.7095957884132167</v>
       </c>
       <c r="F3">
         <v>28.200000000000003</v>
@@ -2882,7 +3925,7 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.0033366151363126</v>
+        <v>4.9699578977173475</v>
       </c>
       <c r="F4">
         <v>24.6</v>
@@ -2915,7 +3958,7 @@
       </c>
       <c r="E5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.881881698168943</v>
+        <v>3.2029638995228402</v>
       </c>
       <c r="F5">
         <v>21.4</v>
@@ -2940,7 +3983,7 @@
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.3443305073286931</v>
+        <v>4.8547439657154445</v>
       </c>
       <c r="F6">
         <v>26.200000000000003</v>
@@ -2965,7 +4008,7 @@
       </c>
       <c r="E7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.4467401747441766</v>
+        <v>4.3064289747389148</v>
       </c>
       <c r="F7">
         <v>29.200000000000003</v>
@@ -2990,7 +4033,7 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6102013621769631</v>
+        <v>3.4256601285009838</v>
       </c>
       <c r="F8">
         <v>21.6</v>
@@ -3015,7 +4058,7 @@
       </c>
       <c r="E9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.781893123384056</v>
+        <v>7.0778241275773652</v>
       </c>
       <c r="F9">
         <v>14.2</v>
@@ -3040,7 +4083,7 @@
       </c>
       <c r="E10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.2408347184285287</v>
+        <v>7.7718210768435725</v>
       </c>
       <c r="F10">
         <v>15.2</v>
@@ -3065,7 +4108,7 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.4099029260760432</v>
+        <v>10.276280325241784</v>
       </c>
       <c r="F11">
         <v>13.100000000000001</v>
@@ -3090,7 +4133,7 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.198330686024249</v>
+        <v>5.5978330941288608</v>
       </c>
       <c r="F12">
         <v>14.100000000000001</v>
@@ -3115,7 +4158,7 @@
       </c>
       <c r="E13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.8728290538969361</v>
+        <v>8.6666405250777352</v>
       </c>
       <c r="F13">
         <v>14.3</v>
@@ -3140,7 +4183,7 @@
       </c>
       <c r="E14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.8939607560292355</v>
+        <v>9.9397158478171583</v>
       </c>
       <c r="F14">
         <v>15.2</v>
@@ -3165,7 +4208,7 @@
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.0418411998536</v>
+        <v>11.526183320662803</v>
       </c>
       <c r="F15">
         <v>19.100000000000001</v>
@@ -3190,7 +4233,7 @@
       </c>
       <c r="E16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.9824680144743567</v>
+        <v>12.442321152332408</v>
       </c>
       <c r="F16">
         <v>27.6</v>
@@ -3215,7 +4258,7 @@
       </c>
       <c r="E17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.85002960294872</v>
+        <v>14.501056799790037</v>
       </c>
       <c r="F17">
         <v>22.2</v>
@@ -3240,7 +4283,7 @@
       </c>
       <c r="E18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.237381215977994</v>
+        <v>13.463676090460151</v>
       </c>
       <c r="F18">
         <v>35.1</v>
@@ -3265,7 +4308,7 @@
       </c>
       <c r="E19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.59520644466159</v>
+        <v>15.131940487488912</v>
       </c>
       <c r="F19">
         <v>32.4</v>
@@ -3290,7 +4333,7 @@
       </c>
       <c r="E20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.436315382084317</v>
+        <v>14.801243356533993</v>
       </c>
       <c r="F20">
         <v>35.1</v>
@@ -3315,7 +4358,7 @@
       </c>
       <c r="E21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.581304581083794</v>
+        <v>12.879261700525404</v>
       </c>
       <c r="F21">
         <v>33.299999999999997</v>
@@ -3340,7 +4383,7 @@
       </c>
       <c r="E22" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.719296715959274</v>
+        <v>15.009082151610302</v>
       </c>
       <c r="F22">
         <v>29.8</v>

--- a/Allgemeine Daten/covariate/generation/flea_jumplength_bloodmeal_raw.xlsx
+++ b/Allgemeine Daten/covariate/generation/flea_jumplength_bloodmeal_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/vorlesungen/Allgemeine Daten/covariate/generation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC3B47D-2436-C447-89EB-7379F59943D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F590EEB-06C0-784B-AF57-66B80E0A9665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2400" yWindow="600" windowWidth="36000" windowHeight="19960" xr2:uid="{A5B12C49-1460-7B46-AA19-811389EE84C0}"/>
   </bookViews>
@@ -892,67 +892,67 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.7591179150939049</c:v>
+                  <c:v>4.0442008195291219</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7095957884132167</c:v>
+                  <c:v>5.931447569656827</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9699578977173475</c:v>
+                  <c:v>6.2596616517336532</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2029638995228402</c:v>
+                  <c:v>6.4404753752599726</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.8547439657154445</c:v>
+                  <c:v>7.5086403082086886</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.3064289747389148</c:v>
+                  <c:v>6.3590183344275015</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.4256601285009838</c:v>
+                  <c:v>6.4569941214014213</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.0778241275773652</c:v>
+                  <c:v>8.7693978067474561</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.7718210768435725</c:v>
+                  <c:v>6.6169119740059363</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.276280325241784</c:v>
+                  <c:v>10.832336387909089</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.5978330941288608</c:v>
+                  <c:v>7.267266148878222</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.6666405250777352</c:v>
+                  <c:v>12.093664388230273</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.9397158478171583</c:v>
+                  <c:v>10.141420762699394</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11.526183320662803</c:v>
+                  <c:v>9.9408642581211542</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12.442321152332408</c:v>
+                  <c:v>13.697677443059881</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>14.501056799790037</c:v>
+                  <c:v>13.882069918410261</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>13.463676090460151</c:v>
+                  <c:v>12.147801196787892</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>15.131940487488912</c:v>
+                  <c:v>16.038821104735497</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>14.801243356533993</c:v>
+                  <c:v>18.584065966099672</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>12.879261700525404</c:v>
+                  <c:v>15.709875418792961</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>15.009082151610302</c:v>
+                  <c:v>13.789475025637124</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E2" s="1">
         <f ca="1">2+1.2*C2+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>3.7591179150939049</v>
+        <v>4.0442008195291219</v>
       </c>
       <c r="F2">
         <v>24.1</v>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:E22" ca="1" si="0">2+1.2*C3+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>1.7095957884132167</v>
+        <v>5.931447569656827</v>
       </c>
       <c r="F3">
         <v>28.200000000000003</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.9699578977173475</v>
+        <v>6.2596616517336532</v>
       </c>
       <c r="F4">
         <v>24.6</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="E5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.2029638995228402</v>
+        <v>6.4404753752599726</v>
       </c>
       <c r="F5">
         <v>21.4</v>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8547439657154445</v>
+        <v>7.5086403082086886</v>
       </c>
       <c r="F6">
         <v>26.200000000000003</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.3064289747389148</v>
+        <v>6.3590183344275015</v>
       </c>
       <c r="F7">
         <v>29.200000000000003</v>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.4256601285009838</v>
+        <v>6.4569941214014213</v>
       </c>
       <c r="F8">
         <v>21.6</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="E9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7.0778241275773652</v>
+        <v>8.7693978067474561</v>
       </c>
       <c r="F9">
         <v>14.2</v>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="E10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7.7718210768435725</v>
+        <v>6.6169119740059363</v>
       </c>
       <c r="F10">
         <v>15.2</v>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.276280325241784</v>
+        <v>10.832336387909089</v>
       </c>
       <c r="F11">
         <v>13.100000000000001</v>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5.5978330941288608</v>
+        <v>7.267266148878222</v>
       </c>
       <c r="F12">
         <v>14.100000000000001</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="E13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.6666405250777352</v>
+        <v>12.093664388230273</v>
       </c>
       <c r="F13">
         <v>14.3</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="E14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.9397158478171583</v>
+        <v>10.141420762699394</v>
       </c>
       <c r="F14">
         <v>15.2</v>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>11.526183320662803</v>
+        <v>9.9408642581211542</v>
       </c>
       <c r="F15">
         <v>19.100000000000001</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="E16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.442321152332408</v>
+        <v>13.697677443059881</v>
       </c>
       <c r="F16">
         <v>27.6</v>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.501056799790037</v>
+        <v>13.882069918410261</v>
       </c>
       <c r="F17">
         <v>22.2</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="E18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.463676090460151</v>
+        <v>12.147801196787892</v>
       </c>
       <c r="F18">
         <v>35.1</v>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.131940487488912</v>
+        <v>16.038821104735497</v>
       </c>
       <c r="F19">
         <v>32.4</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="E20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.801243356533993</v>
+        <v>18.584065966099672</v>
       </c>
       <c r="F20">
         <v>35.1</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="E21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>12.879261700525404</v>
+        <v>15.709875418792961</v>
       </c>
       <c r="F21">
         <v>33.299999999999997</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="E22" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.009082151610302</v>
+        <v>13.789475025637124</v>
       </c>
       <c r="F22">
         <v>29.8</v>
